--- a/owlcms/src/main/resources/templates/weighin/WeighInForm_Horizontal-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/weighin/WeighInForm_Horizontal-LETTER.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ns8="http://schemas.libreoffice.org/" ns1:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns7="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
-  <ns1:AlternateContent>
-    <ns1:Choice Requires="x15">
-      <ns2:absPath url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\weighin\"/>
-    </ns1:Choice>
-  </ns1:AlternateContent>
-  <ns3:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E225AA8-7634-4552-9B56-1A1292ECD058}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1815" windowWidth="29040" windowHeight="15720" tabRatio="500" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1815" windowWidth="29040" windowHeight="15720" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Weigh-in" sheetId="1" ns7:id="rId1"/>
@@ -56,11 +50,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Weigh-in'!$A:$L</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <ns8:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -175,7 +164,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
@@ -864,7 +853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
